--- a/Golden_Set_Preenchido_pelo_RAG.xlsx
+++ b/Golden_Set_Preenchido_pelo_RAG.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="78">
   <si>
     <t>Pergunta</t>
   </si>
@@ -191,79 +191,73 @@
     <t>Diversos pareceres da base abordaram a obrigatoriedade de observação da Instrução Normativa nº 1237, além da mencionada pela resposta da inteligência artificial. Ocaso é que os pareceres não chamaram a exigência de condicionante e a inteligência artificial se prendeu ao texto literal e não interpretou corretamente a exigência como condicionantes.</t>
   </si>
   <si>
-    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Benefício Fiscal/Redução de BC concedida por prazo indeterminado - Art. 8°/XIX/P_104_2022_SEI.docx</t>
-  </si>
-  <si>
-    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Protege/Adicional de 2_/P_037_2018_SEI.doc</t>
-  </si>
-  <si>
-    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/EFD/Informações Gerais/P_202_2024_SEI.docx</t>
-  </si>
-  <si>
-    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Fundeinfra/P_191_2023_SEI.docx</t>
-  </si>
-  <si>
-    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Comércio Exterior/Importação/P_35_2021_SEI.docx</t>
-  </si>
-  <si>
-    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Substituição pela Operação Anterior/Lenha/P_95_2021_SEI.docx</t>
-  </si>
-  <si>
-    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Benefício Fiscal/Crédito Outorgado concedido por pra indeterminado - Art. 11/III/P_037_2019_SEI.doc</t>
-  </si>
-  <si>
-    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Combustível/P_158_2023_SEI.docx</t>
-  </si>
-  <si>
-    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Documentos Fiscais/NF-e/P_034_2018 SEI.doc</t>
-  </si>
-  <si>
-    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Crédito de ICMS/Estorno e Vedação/P_33_2024_SEI.docx</t>
-  </si>
-  <si>
-    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Imunidade/P_28_2021_SEI.docx</t>
-  </si>
-  <si>
-    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Benefício Fiscal/Crédito Outorgado concedido por pra indeterminado - Art. 11/III/P_22_2022_SEI.docx</t>
+    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Benef%C3%ADcio%20Fiscal/Cr%C3%A9dito%20Outorgado%20concedido%20por%20pra%20indeterminado%20-%20Art.%2011/XXXI/P_079_2018%20SEI.docx</t>
+  </si>
+  <si>
+    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/DIFAL%20-%20consumidor%20final%20N%C3%A3o%20contribuinte/C%C3%A1lculo/P_250_2024_SEI.docx</t>
+  </si>
+  <si>
+    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/EFD/Informa%C3%A7%C3%B5es%20Gerais/P_202_2022_SEI.docx</t>
+  </si>
+  <si>
+    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Venda%20de%20Automotor%20Direto%20a%20Consumidor/P_70_2023_SEI.docx</t>
+  </si>
+  <si>
+    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Com%C3%A9rcio%20Exterior/Importa%C3%A7%C3%A3o/P_%20069_2020_SEI.docx</t>
+  </si>
+  <si>
+    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Benef%C3%ADcio%20Fiscal/Isen%C3%A7%C3%A3o%20concedida%20por%20Prazo%20Indeterminado%20-%20Art.%206%C2%BA/LXXVIII/P_282_2023_SEI.docx</t>
+  </si>
+  <si>
+    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Benef%C3%ADcio%20Fiscal/Redu%C3%A7%C3%A3o%20de%20BC%20concedida%20por%20prazo%20indeterminado%20-%20Art.%208%C2%B0/VIII/P_27_2021_SEI.docx</t>
+  </si>
+  <si>
+    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Combust%C3%ADvel/P_127_2023_SEI.docx</t>
+  </si>
+  <si>
+    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Programa%20Produzir/Comexproduzir/P_24_2021_SEI.docx</t>
+  </si>
+  <si>
+    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Fundeinfra/P_82_2023_SEI.docx</t>
+  </si>
+  <si>
+    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/DIFAL%20-%20Uso%20e%20Consumo%20e%20Ativo%20Imobilizado/Obrigatoriedade/P_176_2021_SEI.docx</t>
+  </si>
+  <si>
+    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Benef%C3%ADcio%20Fiscal/Isen%C3%A7%C3%A3o%20concedida%20por%20Prazo%20Indeterminado%20-%20Art.%206%C2%BA/XLIX/P_69_2023_SEI.docx</t>
   </si>
   <si>
     <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Fundeinfra/P_185_2023_SEI.docx</t>
   </si>
   <si>
-    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Crédito de ICMS/Informações Gerais/P_80_2022_SEI.docx</t>
-  </si>
-  <si>
-    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Fundeinfra/P_84_2024_SEI.docx</t>
-  </si>
-  <si>
-    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Decreto nº 4.852-97 - RCTE - Informações Gerais/P_29_2021_SEI.docx</t>
-  </si>
-  <si>
-    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Imunidade/P_47_2021_SEI.docx</t>
-  </si>
-  <si>
-    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Venda fora do Estabelecimento/P_278_2021_SEI.docx</t>
-  </si>
-  <si>
-    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Benefício Fiscal/Redução de BC concedida por prazo indeterminado - Art. 8°/LVII/P_51_2023_SEI.docx</t>
-  </si>
-  <si>
-    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Benefício Fiscal/Redução de BC concedida por prazo determinado - Art. 9°/VIII/P_24_2023_SEI.docx</t>
-  </si>
-  <si>
-    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Decreto nº 4.852-97 - RCTE - Informações Gerais/P_246_2024_SEI.docx</t>
-  </si>
-  <si>
-    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/PróGoiás/P_44_2023_SEI.docx</t>
-  </si>
-  <si>
-    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Benefício Fiscal/Isenção concedida por Prazo Indeterminado - Art. 6º/CXVI/P_231_2023_SEI.docx</t>
-  </si>
-  <si>
-    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Benefício Fiscal/Redução de BC concedida por prazo determinado - Art. 9°/XXXVIII/P_24_2023_SEI.docx</t>
-  </si>
-  <si>
-    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Pauta de Valores de mercadorias/P_48_2021_SEI.docx</t>
+    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Programa%20Produzir/Informa%C3%A7%C3%B5es%20Gerais/P_43_2024_SEI.docx</t>
+  </si>
+  <si>
+    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Recupera%C3%A7%C3%A3o%20de%20Cr%C3%A9dito/Lei%20n%2022.935_24%20%20Convalida%C3%A7%C3%A3o%20dos%20Benef%C3%ADcos%20sem%20cumprimento%20das%20condicionantes/P_22_2025_SEI.docx</t>
+  </si>
+  <si>
+    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Benef%C3%ADcio%20Fiscal/Isen%C3%A7%C3%A3o%20concedida%20por%20Prazo%20Indeterminado%20-%20Art.%206%C2%BA/CXXII/P_82_2025_SEI.docx</t>
+  </si>
+  <si>
+    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/IPVA/Informa%C3%A7%C3%B5es%20Gerais/P_126_2023_SEI.docx</t>
+  </si>
+  <si>
+    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Benef%C3%ADcio%20Fiscal/Cr%C3%A9dito%20Outorgado%20concedido%20por%20pra%20indeterminado%20-%20Art.%2011/XXXIV/P_17_2023_SEI.docx</t>
+  </si>
+  <si>
+    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Programa%20Produzir/Informa%C3%A7%C3%B5es%20Gerais/P_54_2021_SEI.docx</t>
+  </si>
+  <si>
+    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/IPVA/Al%C3%ADquotas-Base%20de%20C%C3%A1lculo/P_47_2023_SEI.docx</t>
+  </si>
+  <si>
+    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Benef%C3%ADcio%20Fiscal/Cr%C3%A9dito%20Outorgado%20concedido%20por%20pra%20indeterminado%20-%20Art.%2011/V/P_231_2023_SEI.docx</t>
+  </si>
+  <si>
+    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Benef%C3%ADcio%20Fiscal/Redu%C3%A7%C3%A3o%20de%20BC%20concedida%20por%20prazo%20indeterminado%20-%20Art.%208%C2%B0/VIII/P_232_2024_SEI.docx</t>
+  </si>
+  <si>
+    <t>https://appasp.economia.go.gov.br/pareceres/arquivos/Benef%C3%ADcio%20Fiscal/Isen%C3%A7%C3%A3o%20concedida%20por%20Prazo%20Indeterminado%20-%20Art.%206%C2%BA/XV/P_110_2025_SEI.docx</t>
   </si>
 </sst>
 </file>
@@ -777,7 +771,7 @@
         <v>40</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -799,7 +793,7 @@
         <v>41</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -810,7 +804,7 @@
         <v>42</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -821,7 +815,7 @@
         <v>43</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -832,7 +826,7 @@
         <v>44</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -843,7 +837,7 @@
         <v>45</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -854,7 +848,7 @@
         <v>46</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -865,7 +859,7 @@
         <v>47</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -876,7 +870,7 @@
         <v>48</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -887,7 +881,7 @@
         <v>49</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -898,7 +892,7 @@
         <v>50</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -909,7 +903,7 @@
         <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -920,7 +914,7 @@
         <v>52</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -931,7 +925,7 @@
         <v>53</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -942,7 +936,7 @@
         <v>54</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
